--- a/data/department_schedules_finals/faculty_schedule_manuel_finals.xlsx
+++ b/data/department_schedules_finals/faculty_schedule_manuel_finals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22376D0C-982F-488E-BC53-F0192F7C6457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE160B1A-DA66-4368-8CFA-FFBF8E3025FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35520" yWindow="13725" windowWidth="24465" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,14 +33,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="299">
   <si>
     <t>Departments</t>
   </si>
   <si>
-    <t>Year:</t>
-  </si>
-  <si>
     <t>Course ID</t>
   </si>
   <si>
@@ -932,19 +929,7 @@
     <t>Utilization</t>
   </si>
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Running Total</t>
-  </si>
-  <si>
-    <t>Count</t>
+    <t>Year</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1110,7 @@
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{32036BC4-45EB-48F8-BFCA-0492E03A7C3D}" name="Departments" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{7C17D98E-3278-4EA5-8F87-10A437BA0848}" name="Year:" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{7C17D98E-3278-4EA5-8F87-10A437BA0848}" name="Year" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{6F72E20A-4326-4C67-89B4-8AB845C22871}" name="Course ID" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{32239187-08E0-47B7-BE19-DF63674ECF9C}" name="Day" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{7B3CF146-7378-457C-9A93-238A60E437B1}" name="Assigned Rooms" dataDxfId="5"/>
@@ -1443,45 +1428,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>298</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1499,19 +1484,19 @@
     </row>
     <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F3" s="2">
         <v>4</v>
@@ -1529,19 +1514,19 @@
     </row>
     <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -1559,19 +1544,19 @@
     </row>
     <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -1589,19 +1574,19 @@
     </row>
     <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -1619,19 +1604,19 @@
     </row>
     <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -1649,19 +1634,19 @@
     </row>
     <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -1679,19 +1664,19 @@
     </row>
     <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2">
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
@@ -1709,19 +1694,19 @@
     </row>
     <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2">
         <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F10" s="2">
         <v>1</v>
@@ -1739,19 +1724,19 @@
     </row>
     <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F11" s="2">
         <v>2</v>
@@ -1769,19 +1754,19 @@
     </row>
     <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2">
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F12" s="2">
         <v>2</v>
@@ -1799,19 +1784,19 @@
     </row>
     <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2">
         <v>2</v>
@@ -1829,19 +1814,19 @@
     </row>
     <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F14" s="2">
         <v>3</v>
@@ -1859,19 +1844,19 @@
     </row>
     <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F15" s="2">
         <v>3</v>
@@ -1889,19 +1874,19 @@
     </row>
     <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F16" s="2">
         <v>2</v>
@@ -1919,19 +1904,19 @@
     </row>
     <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F17" s="2">
         <v>3</v>
@@ -1949,19 +1934,19 @@
     </row>
     <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F18" s="2">
         <v>4</v>
@@ -1979,19 +1964,19 @@
     </row>
     <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F19" s="2">
         <v>3</v>
@@ -2009,19 +1994,19 @@
     </row>
     <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2">
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F20" s="2">
         <v>2</v>
@@ -2039,19 +2024,19 @@
     </row>
     <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2">
         <v>4</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F21" s="2">
         <v>2</v>
@@ -2069,19 +2054,19 @@
     </row>
     <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F22" s="2">
         <v>4</v>
@@ -2099,19 +2084,19 @@
     </row>
     <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
@@ -2129,19 +2114,19 @@
     </row>
     <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B24" s="2">
         <v>4</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
@@ -2159,19 +2144,19 @@
     </row>
     <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" s="2">
         <v>4</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F25" s="2">
         <v>1</v>
@@ -2189,19 +2174,19 @@
     </row>
     <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" s="2">
         <v>4</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F26" s="2">
         <v>2</v>
@@ -2219,19 +2204,19 @@
     </row>
     <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" s="2">
         <v>2</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F27" s="2">
         <v>2</v>
@@ -2249,19 +2234,19 @@
     </row>
     <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F28" s="2">
         <v>4</v>
@@ -2279,19 +2264,19 @@
     </row>
     <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29" s="2">
         <v>2</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D29" s="2">
         <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F29" s="2">
         <v>4</v>
@@ -2309,19 +2294,19 @@
     </row>
     <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30" s="2">
         <v>3</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F30" s="2">
         <v>4</v>
@@ -2339,19 +2324,19 @@
     </row>
     <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B31" s="2">
         <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F31" s="2">
         <v>5</v>
@@ -2369,19 +2354,19 @@
     </row>
     <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B32" s="2">
         <v>2</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D32" s="2">
         <v>1</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -2399,19 +2384,19 @@
     </row>
     <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B33" s="2">
         <v>1</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" s="2">
         <v>1</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F33" s="2">
         <v>1</v>
@@ -2429,19 +2414,19 @@
     </row>
     <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B34" s="2">
         <v>4</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F34" s="2">
         <v>1</v>
@@ -2459,19 +2444,19 @@
     </row>
     <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" s="2">
         <v>4</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F35" s="2">
         <v>1</v>
@@ -2489,19 +2474,19 @@
     </row>
     <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B36" s="2">
         <v>3</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D36" s="2">
         <v>2</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F36" s="2">
         <v>1</v>
@@ -2519,19 +2504,19 @@
     </row>
     <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B37" s="2">
         <v>4</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D37" s="2">
         <v>2</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F37" s="2">
         <v>1</v>
@@ -2549,19 +2534,19 @@
     </row>
     <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" s="2">
         <v>1</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D38" s="2">
         <v>2</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F38" s="2">
         <v>1</v>
@@ -2579,19 +2564,19 @@
     </row>
     <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39" s="2">
         <v>2</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D39" s="2">
         <v>2</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F39" s="2">
         <v>1</v>
@@ -2609,19 +2594,19 @@
     </row>
     <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2">
         <v>2</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D40" s="2">
         <v>2</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -2639,19 +2624,19 @@
     </row>
     <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B41" s="2">
         <v>4</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D41" s="2">
         <v>2</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F41" s="2">
         <v>1</v>
@@ -2669,19 +2654,19 @@
     </row>
     <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B42" s="2">
         <v>1</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D42" s="2">
         <v>2</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F42" s="2">
         <v>2</v>
@@ -2699,19 +2684,19 @@
     </row>
     <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B43" s="2">
         <v>3</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D43" s="2">
         <v>2</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F43" s="2">
         <v>2</v>
@@ -2729,19 +2714,19 @@
     </row>
     <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B44" s="2">
         <v>4</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D44" s="2">
         <v>2</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F44" s="2">
         <v>2</v>
@@ -2759,19 +2744,19 @@
     </row>
     <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B45" s="2">
         <v>3</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D45" s="2">
         <v>2</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F45" s="2">
         <v>1</v>
@@ -2789,19 +2774,19 @@
     </row>
     <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B46" s="2">
         <v>2</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D46" s="2">
         <v>2</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
@@ -2819,19 +2804,19 @@
     </row>
     <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B47" s="2">
         <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D47" s="2">
         <v>2</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -2849,19 +2834,19 @@
     </row>
     <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48" s="2">
         <v>2</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D48" s="2">
         <v>2</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F48" s="2">
         <v>5</v>
@@ -2879,19 +2864,19 @@
     </row>
     <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" s="2">
         <v>4</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D49" s="2">
         <v>2</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F49" s="2">
         <v>1</v>
@@ -2909,19 +2894,19 @@
     </row>
     <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50" s="2">
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D50" s="2">
         <v>2</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F50" s="2">
         <v>3</v>
@@ -2939,19 +2924,19 @@
     </row>
     <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B51" s="2">
         <v>1</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D51" s="2">
         <v>2</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F51" s="2">
         <v>3</v>
@@ -2969,19 +2954,19 @@
     </row>
     <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52" s="2">
         <v>1</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D52" s="2">
         <v>2</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F52" s="2">
         <v>3</v>
@@ -2999,19 +2984,19 @@
     </row>
     <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B53" s="2">
         <v>4</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D53" s="2">
         <v>2</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F53" s="2">
         <v>2</v>
@@ -3029,19 +3014,19 @@
     </row>
     <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B54" s="2">
         <v>4</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D54" s="2">
         <v>2</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F54" s="2">
         <v>1</v>
@@ -3059,19 +3044,19 @@
     </row>
     <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B55" s="2">
         <v>3</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D55" s="2">
         <v>2</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F55" s="2">
         <v>3</v>
@@ -3089,19 +3074,19 @@
     </row>
     <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B56" s="2">
         <v>4</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D56" s="2">
         <v>2</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F56" s="2">
         <v>1</v>
@@ -3119,19 +3104,19 @@
     </row>
     <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B57" s="2">
         <v>4</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D57" s="2">
         <v>2</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F57" s="2">
         <v>2</v>
@@ -3149,19 +3134,19 @@
     </row>
     <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" s="2">
         <v>4</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D58" s="2">
         <v>2</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F58" s="2">
         <v>2</v>
@@ -3179,19 +3164,19 @@
     </row>
     <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59" s="2">
         <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D59" s="2">
         <v>2</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F59" s="2">
         <v>3</v>
@@ -3209,19 +3194,19 @@
     </row>
     <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B60" s="2">
         <v>4</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D60" s="2">
         <v>2</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F60" s="2">
         <v>2</v>
@@ -3239,19 +3224,19 @@
     </row>
     <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B61" s="2">
         <v>3</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D61" s="2">
         <v>2</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F61" s="2">
         <v>1</v>
@@ -3269,19 +3254,19 @@
     </row>
     <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B62" s="2">
         <v>1</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D62" s="2">
         <v>2</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F62" s="2">
         <v>2</v>
@@ -3299,19 +3284,19 @@
     </row>
     <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B63" s="2">
         <v>4</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D63" s="2">
         <v>2</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F63" s="2">
         <v>1</v>
@@ -3329,19 +3314,19 @@
     </row>
     <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B64" s="2">
         <v>4</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D64" s="2">
         <v>2</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F64" s="2">
         <v>1</v>
@@ -3359,19 +3344,19 @@
     </row>
     <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B65" s="2">
         <v>4</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D65" s="2">
         <v>2</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F65" s="2">
         <v>1</v>
@@ -3389,19 +3374,19 @@
     </row>
     <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B66" s="2">
         <v>4</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D66" s="2">
         <v>2</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F66" s="2">
         <v>1</v>
@@ -3419,19 +3404,19 @@
     </row>
     <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B67" s="2">
         <v>1</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D67" s="2">
         <v>3</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F67" s="2">
         <v>7</v>
@@ -3449,19 +3434,19 @@
     </row>
     <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B68" s="2">
         <v>3</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D68" s="2">
         <v>3</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F68" s="2">
         <v>4</v>
@@ -3479,19 +3464,19 @@
     </row>
     <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B69" s="2">
         <v>2</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D69" s="2">
         <v>3</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F69" s="2">
         <v>1</v>
@@ -3509,19 +3494,19 @@
     </row>
     <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B70" s="2">
         <v>3</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D70" s="2">
         <v>3</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F70" s="2">
         <v>1</v>
@@ -3539,19 +3524,19 @@
     </row>
     <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B71" s="2">
         <v>4</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D71" s="2">
         <v>3</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F71" s="2">
         <v>1</v>
@@ -3569,19 +3554,19 @@
     </row>
     <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B72" s="2">
         <v>1</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D72" s="2">
         <v>3</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F72" s="2">
         <v>1</v>
@@ -3599,19 +3584,19 @@
     </row>
     <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B73" s="2">
         <v>4</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D73" s="2">
         <v>3</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F73" s="2">
         <v>1</v>
@@ -3629,19 +3614,19 @@
     </row>
     <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B74" s="2">
         <v>2</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D74" s="2">
         <v>3</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F74" s="2">
         <v>1</v>
@@ -3659,19 +3644,19 @@
     </row>
     <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B75" s="2">
         <v>3</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D75" s="2">
         <v>3</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F75" s="2">
         <v>1</v>
@@ -3689,19 +3674,19 @@
     </row>
     <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B76" s="2">
         <v>3</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D76" s="2">
         <v>3</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F76" s="2">
         <v>1</v>
@@ -3719,19 +3704,19 @@
     </row>
     <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B77" s="2">
         <v>4</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D77" s="2">
         <v>3</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F77" s="2">
         <v>1</v>
@@ -3749,19 +3734,19 @@
     </row>
     <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B78" s="2">
         <v>2</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D78" s="2">
         <v>3</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F78" s="2">
         <v>2</v>
@@ -3779,19 +3764,19 @@
     </row>
     <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B79" s="2">
         <v>4</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D79" s="2">
         <v>3</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F79" s="2">
         <v>2</v>
@@ -3809,19 +3794,19 @@
     </row>
     <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80" s="2">
         <v>4</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D80" s="2">
         <v>3</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F80" s="2">
         <v>1</v>
@@ -3839,19 +3824,19 @@
     </row>
     <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81" s="2">
         <v>4</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D81" s="2">
         <v>3</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F81" s="2">
         <v>1</v>
@@ -3869,19 +3854,19 @@
     </row>
     <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" s="2">
         <v>3</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D82" s="2">
         <v>3</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F82" s="2">
         <v>4</v>
@@ -3899,19 +3884,19 @@
     </row>
     <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B83" s="2">
         <v>2</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D83" s="2">
         <v>3</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F83" s="2">
         <v>3</v>
@@ -3929,19 +3914,19 @@
     </row>
     <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B84" s="2">
         <v>2</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D84" s="2">
         <v>3</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F84" s="2">
         <v>2</v>
@@ -3959,19 +3944,19 @@
     </row>
     <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B85" s="2">
         <v>4</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D85" s="2">
         <v>3</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F85" s="2">
         <v>1</v>
@@ -3989,19 +3974,19 @@
     </row>
     <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B86" s="2">
         <v>1</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D86" s="2">
         <v>3</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F86" s="2">
         <v>3</v>
@@ -4019,19 +4004,19 @@
     </row>
     <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B87" s="2">
         <v>1</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D87" s="2">
         <v>3</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F87" s="2">
         <v>2</v>
@@ -4049,19 +4034,19 @@
     </row>
     <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B88" s="2">
         <v>4</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D88" s="2">
         <v>3</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F88" s="2">
         <v>2</v>
@@ -4079,19 +4064,19 @@
     </row>
     <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B89" s="2">
         <v>3</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D89" s="2">
         <v>3</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F89" s="2">
         <v>2</v>
@@ -4109,19 +4094,19 @@
     </row>
     <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B90" s="2">
         <v>3</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D90" s="2">
         <v>3</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F90" s="2">
         <v>3</v>
@@ -4139,19 +4124,19 @@
     </row>
     <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B91" s="2">
         <v>1</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D91" s="2">
         <v>3</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F91" s="2">
         <v>9</v>
@@ -4169,19 +4154,19 @@
     </row>
     <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B92" s="2">
         <v>2</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D92" s="2">
         <v>3</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F92" s="2">
         <v>4</v>
@@ -4199,19 +4184,19 @@
     </row>
     <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B93" s="2">
         <v>4</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D93" s="2">
         <v>3</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F93" s="2">
         <v>1</v>
@@ -4229,19 +4214,19 @@
     </row>
     <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B94" s="2">
         <v>3</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D94" s="2">
         <v>3</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F94" s="2">
         <v>1</v>
@@ -4259,19 +4244,19 @@
     </row>
     <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B95" s="2">
         <v>2</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D95" s="2">
         <v>3</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F95" s="2">
         <v>1</v>
@@ -4289,19 +4274,19 @@
     </row>
     <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B96" s="2">
         <v>1</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D96" s="2">
         <v>4</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F96" s="2">
         <v>1</v>
@@ -4319,19 +4304,19 @@
     </row>
     <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B97" s="2">
         <v>2</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D97" s="2">
         <v>4</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F97" s="2">
         <v>1</v>
@@ -4349,19 +4334,19 @@
     </row>
     <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B98" s="2">
         <v>3</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D98" s="2">
         <v>4</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F98" s="2">
         <v>1</v>
@@ -4379,19 +4364,19 @@
     </row>
     <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B99" s="2">
         <v>4</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D99" s="2">
         <v>4</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F99" s="2">
         <v>1</v>
@@ -4409,19 +4394,19 @@
     </row>
     <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B100" s="2">
         <v>4</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D100" s="2">
         <v>4</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F100" s="2">
         <v>1</v>
@@ -4439,19 +4424,19 @@
     </row>
     <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B101" s="2">
         <v>3</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D101" s="2">
         <v>4</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F101" s="2">
         <v>1</v>
@@ -4469,19 +4454,19 @@
     </row>
     <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B102" s="2">
         <v>4</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D102" s="2">
         <v>4</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F102" s="2">
         <v>1</v>
@@ -4499,19 +4484,19 @@
     </row>
     <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B103" s="2">
         <v>2</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D103" s="2">
         <v>4</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F103" s="2">
         <v>3</v>
@@ -4529,19 +4514,19 @@
     </row>
     <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B104" s="2">
         <v>4</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D104" s="2">
         <v>4</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F104" s="2">
         <v>1</v>
@@ -4559,19 +4544,19 @@
     </row>
     <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B105" s="2">
         <v>2</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D105" s="2">
         <v>4</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F105" s="2">
         <v>1</v>
@@ -4589,19 +4574,19 @@
     </row>
     <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B106" s="2">
         <v>3</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D106" s="2">
         <v>4</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F106" s="2">
         <v>1</v>
@@ -4619,19 +4604,19 @@
     </row>
     <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B107" s="2">
         <v>3</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D107" s="2">
         <v>4</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F107" s="2">
         <v>1</v>
@@ -4649,19 +4634,19 @@
     </row>
     <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B108" s="2">
         <v>1</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D108" s="2">
         <v>4</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F108" s="2">
         <v>6</v>
@@ -4679,19 +4664,19 @@
     </row>
     <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B109" s="2">
         <v>4</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D109" s="2">
         <v>4</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F109" s="2">
         <v>1</v>
@@ -4709,19 +4694,19 @@
     </row>
     <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B110" s="2">
         <v>4</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D110" s="2">
         <v>4</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F110" s="2">
         <v>3</v>
@@ -4739,19 +4724,19 @@
     </row>
     <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B111" s="2">
         <v>3</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D111" s="2">
         <v>4</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F111" s="2">
         <v>3</v>
@@ -4769,19 +4754,19 @@
     </row>
     <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B112" s="2">
         <v>3</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D112" s="2">
         <v>4</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F112" s="2">
         <v>1</v>
@@ -4799,19 +4784,19 @@
     </row>
     <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B113" s="2">
         <v>1</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D113" s="2">
         <v>4</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F113" s="2">
         <v>1</v>
@@ -4829,19 +4814,19 @@
     </row>
     <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B114" s="2">
         <v>3</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D114" s="2">
         <v>4</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F114" s="2">
         <v>1</v>
@@ -4859,19 +4844,19 @@
     </row>
     <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B115" s="2">
         <v>3</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D115" s="2">
         <v>4</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F115" s="2">
         <v>1</v>
@@ -4889,19 +4874,19 @@
     </row>
     <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B116" s="2">
         <v>4</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D116" s="2">
         <v>4</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F116" s="2">
         <v>1</v>
@@ -4919,19 +4904,19 @@
     </row>
     <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B117" s="2">
         <v>4</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D117" s="2">
         <v>4</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F117" s="2">
         <v>1</v>
@@ -4949,19 +4934,19 @@
     </row>
     <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B118" s="2">
         <v>4</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D118" s="2">
         <v>4</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F118" s="2">
         <v>1</v>
@@ -4979,19 +4964,19 @@
     </row>
     <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B119" s="2">
         <v>4</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D119" s="2">
         <v>4</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F119" s="2">
         <v>2</v>
@@ -5009,19 +4994,19 @@
     </row>
     <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B120" s="2">
         <v>3</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D120" s="2">
         <v>4</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F120" s="2">
         <v>2</v>
@@ -5039,19 +5024,19 @@
     </row>
     <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B121" s="2">
         <v>3</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D121" s="2">
         <v>4</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F121" s="2">
         <v>2</v>
@@ -5069,19 +5054,19 @@
     </row>
     <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B122" s="2">
         <v>4</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D122" s="2">
         <v>4</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F122" s="2">
         <v>1</v>
@@ -5099,19 +5084,19 @@
     </row>
     <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B123" s="2">
         <v>2</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D123" s="2">
         <v>4</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F123" s="2">
         <v>3</v>
@@ -5129,19 +5114,19 @@
     </row>
     <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B124" s="2">
         <v>3</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D124" s="2">
         <v>4</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F124" s="2">
         <v>1</v>
@@ -5159,19 +5144,19 @@
     </row>
     <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B125" s="2">
         <v>2</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D125" s="2">
         <v>4</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F125" s="2">
         <v>4</v>
@@ -5189,19 +5174,19 @@
     </row>
     <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B126" s="2">
         <v>4</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D126" s="2">
         <v>4</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F126" s="2">
         <v>1</v>
@@ -5219,19 +5204,19 @@
     </row>
     <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B127" s="2">
         <v>4</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D127" s="2">
         <v>4</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F127" s="2">
         <v>1</v>
@@ -5249,19 +5234,19 @@
     </row>
     <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B128" s="2">
         <v>1</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D128" s="2">
         <v>5</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F128" s="2">
         <v>3</v>
@@ -5279,19 +5264,19 @@
     </row>
     <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B129" s="2">
         <v>1</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D129" s="2">
         <v>5</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F129" s="2">
         <v>4</v>
@@ -5309,19 +5294,19 @@
     </row>
     <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B130" s="2">
         <v>2</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D130" s="2">
         <v>5</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F130" s="2">
         <v>5</v>
@@ -5339,19 +5324,19 @@
     </row>
     <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B131" s="2">
         <v>2</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D131" s="2">
         <v>5</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F131" s="2">
         <v>1</v>
@@ -5369,19 +5354,19 @@
     </row>
     <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B132" s="2">
         <v>3</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D132" s="2">
         <v>5</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F132" s="2">
         <v>1</v>
@@ -5399,19 +5384,19 @@
     </row>
     <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B133" s="2">
         <v>1</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D133" s="2">
         <v>5</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F133" s="2">
         <v>1</v>
@@ -5429,19 +5414,19 @@
     </row>
     <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B134" s="2">
         <v>2</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D134" s="2">
         <v>5</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F134" s="2">
         <v>1</v>
@@ -5459,19 +5444,19 @@
     </row>
     <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B135" s="2">
         <v>3</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D135" s="2">
         <v>5</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F135" s="2">
         <v>1</v>
@@ -5489,19 +5474,19 @@
     </row>
     <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B136" s="2">
         <v>4</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D136" s="2">
         <v>5</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F136" s="2">
         <v>1</v>
@@ -5519,19 +5504,19 @@
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B137" s="2">
         <v>2</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D137" s="2">
         <v>5</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F137" s="2">
         <v>2</v>
@@ -5549,19 +5534,19 @@
     </row>
     <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B138" s="2">
         <v>2</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D138" s="2">
         <v>5</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F138" s="2">
         <v>2</v>
@@ -5579,19 +5564,19 @@
     </row>
     <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B139" s="2">
         <v>2</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D139" s="2">
         <v>5</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F139" s="2">
         <v>1</v>
@@ -5609,19 +5594,19 @@
     </row>
     <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B140" s="2">
         <v>4</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D140" s="2">
         <v>5</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F140" s="2">
         <v>1</v>
@@ -5639,19 +5624,19 @@
     </row>
     <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B141" s="2">
         <v>3</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D141" s="2">
         <v>5</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F141" s="2">
         <v>4</v>
@@ -5669,19 +5654,19 @@
     </row>
     <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B142" s="2">
         <v>2</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D142" s="2">
         <v>5</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F142" s="2">
         <v>3</v>
@@ -5699,19 +5684,19 @@
     </row>
     <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B143" s="2">
         <v>2</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D143" s="2">
         <v>5</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F143" s="2">
         <v>3</v>
@@ -5729,19 +5714,19 @@
     </row>
     <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B144" s="2">
         <v>3</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D144" s="2">
         <v>5</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F144" s="2">
         <v>2</v>
@@ -5759,19 +5744,19 @@
     </row>
     <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B145" s="2">
         <v>1</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D145" s="2">
         <v>5</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F145" s="2">
         <v>4</v>
@@ -5789,19 +5774,19 @@
     </row>
     <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B146" s="2">
         <v>4</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D146" s="2">
         <v>5</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F146" s="2">
         <v>1</v>
@@ -5819,19 +5804,19 @@
     </row>
     <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B147" s="2">
         <v>4</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D147" s="2">
         <v>5</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F147" s="2">
         <v>1</v>
@@ -5849,19 +5834,19 @@
     </row>
     <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B148" s="2">
         <v>4</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D148" s="2">
         <v>5</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F148" s="2">
         <v>2</v>
@@ -5879,19 +5864,19 @@
     </row>
     <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B149" s="2">
         <v>2</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D149" s="2">
         <v>5</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F149" s="2">
         <v>3</v>
@@ -5909,19 +5894,19 @@
     </row>
     <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B150" s="2">
         <v>3</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D150" s="2">
         <v>5</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F150" s="2">
         <v>3</v>
@@ -5939,19 +5924,19 @@
     </row>
     <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B151" s="2">
         <v>2</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D151" s="2">
         <v>6</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F151" s="2">
         <v>2</v>
@@ -5969,19 +5954,19 @@
     </row>
     <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B152" s="2">
         <v>3</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D152" s="2">
         <v>6</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F152" s="2">
         <v>1</v>
@@ -5999,19 +5984,19 @@
     </row>
     <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B153" s="2">
         <v>1</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D153" s="2">
         <v>6</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F153" s="2">
         <v>1</v>
@@ -6029,19 +6014,19 @@
     </row>
     <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B154" s="2">
         <v>2</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D154" s="2">
         <v>6</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F154" s="2">
         <v>1</v>
@@ -6059,19 +6044,19 @@
     </row>
     <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B155" s="2">
         <v>3</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D155" s="2">
         <v>6</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F155" s="2">
         <v>1</v>
@@ -6089,19 +6074,19 @@
     </row>
     <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B156" s="2">
         <v>3</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D156" s="2">
         <v>6</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F156" s="2">
         <v>1</v>
@@ -6119,19 +6104,19 @@
     </row>
     <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B157" s="2">
         <v>4</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D157" s="2">
         <v>6</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F157" s="2">
         <v>1</v>
@@ -6149,19 +6134,19 @@
     </row>
     <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B158" s="2">
         <v>4</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D158" s="2">
         <v>6</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F158" s="2">
         <v>1</v>
@@ -6179,19 +6164,19 @@
     </row>
     <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B159" s="2">
         <v>1</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D159" s="2">
         <v>6</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F159" s="2">
         <v>3</v>
@@ -6209,19 +6194,19 @@
     </row>
     <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B160" s="2">
         <v>2</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D160" s="2">
         <v>6</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F160" s="2">
         <v>4</v>
@@ -6239,19 +6224,19 @@
     </row>
     <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B161" s="2">
         <v>2</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D161" s="2">
         <v>6</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F161" s="2">
         <v>4</v>
@@ -6269,19 +6254,19 @@
     </row>
     <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B162" s="2">
         <v>4</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D162" s="2">
         <v>6</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F162" s="2">
         <v>1</v>
@@ -6299,19 +6284,19 @@
     </row>
     <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B163" s="2">
         <v>4</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D163" s="2">
         <v>6</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F163" s="2">
         <v>1</v>
@@ -6329,19 +6314,19 @@
     </row>
     <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B164" s="2">
         <v>1</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D164" s="2">
         <v>6</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F164" s="2">
         <v>4</v>
@@ -6359,19 +6344,19 @@
     </row>
     <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B165" s="2">
         <v>4</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D165" s="2">
         <v>6</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F165" s="2">
         <v>1</v>
@@ -6389,19 +6374,19 @@
     </row>
     <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B166" s="2">
         <v>4</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D166" s="2">
         <v>6</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F166" s="2">
         <v>1</v>
@@ -6419,19 +6404,19 @@
     </row>
     <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B167" s="2">
         <v>1</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D167" s="2">
         <v>6</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F167" s="2">
         <v>3</v>
@@ -6449,19 +6434,19 @@
     </row>
     <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B168" s="2">
         <v>2</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D168" s="2">
         <v>6</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F168" s="2">
         <v>3</v>
@@ -6479,19 +6464,19 @@
     </row>
     <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B169" s="2">
         <v>3</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D169" s="2">
         <v>6</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F169" s="2">
         <v>2</v>
@@ -6509,19 +6494,19 @@
     </row>
     <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B170" s="2">
         <v>3</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D170" s="2">
         <v>6</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F170" s="2">
         <v>1</v>
@@ -6539,19 +6524,19 @@
     </row>
     <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B171" s="2">
         <v>3</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D171" s="2">
         <v>6</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F171" s="2">
         <v>2</v>
@@ -6569,19 +6554,19 @@
     </row>
     <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B172" s="2">
         <v>3</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D172" s="2">
         <v>6</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F172" s="2">
         <v>2</v>
@@ -6599,19 +6584,19 @@
     </row>
     <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B173" s="2">
         <v>1</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D173" s="2">
         <v>7</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F173" s="2">
         <v>3</v>
@@ -6629,19 +6614,19 @@
     </row>
     <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B174" s="2">
         <v>3</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D174" s="2">
         <v>7</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F174" s="2">
         <v>2</v>
@@ -6659,19 +6644,19 @@
     </row>
     <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B175" s="2">
         <v>3</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D175" s="2">
         <v>7</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F175" s="2">
         <v>1</v>
@@ -6689,19 +6674,19 @@
     </row>
     <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B176" s="2">
         <v>4</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D176" s="2">
         <v>7</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F176" s="2">
         <v>1</v>
@@ -6719,19 +6704,19 @@
     </row>
     <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B177" s="2">
         <v>1</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D177" s="2">
         <v>7</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F177" s="2">
         <v>1</v>
@@ -6749,19 +6734,19 @@
     </row>
     <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B178" s="2">
         <v>2</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D178" s="2">
         <v>7</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F178" s="2">
         <v>1</v>
@@ -6779,19 +6764,19 @@
     </row>
     <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B179" s="2">
         <v>3</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D179" s="2">
         <v>7</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F179" s="2">
         <v>1</v>
@@ -6809,19 +6794,19 @@
     </row>
     <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B180" s="2">
         <v>1</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D180" s="2">
         <v>7</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F180" s="2">
         <v>3</v>
@@ -6839,19 +6824,19 @@
     </row>
     <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B181" s="2">
         <v>2</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D181" s="2">
         <v>7</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F181" s="2">
         <v>2</v>
@@ -6869,19 +6854,19 @@
     </row>
     <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B182" s="2">
         <v>3</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D182" s="2">
         <v>7</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F182" s="2">
         <v>2</v>
@@ -6899,19 +6884,19 @@
     </row>
     <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B183" s="2">
         <v>4</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D183" s="2">
         <v>7</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F183" s="2">
         <v>1</v>
@@ -6929,19 +6914,19 @@
     </row>
     <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B184" s="2">
         <v>2</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D184" s="2">
         <v>7</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F184" s="2">
         <v>4</v>
@@ -6959,19 +6944,19 @@
     </row>
     <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B185" s="2">
         <v>1</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D185" s="2">
         <v>7</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F185" s="2">
         <v>3</v>
@@ -6989,19 +6974,19 @@
     </row>
     <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B186" s="2">
         <v>3</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D186" s="2">
         <v>7</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F186" s="2">
         <v>4</v>
@@ -7019,19 +7004,19 @@
     </row>
     <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B187" s="2">
         <v>3</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D187" s="2">
         <v>7</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F187" s="2">
         <v>1</v>
@@ -7049,19 +7034,19 @@
     </row>
     <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B188" s="2">
         <v>4</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D188" s="2">
         <v>7</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F188" s="2">
         <v>1</v>
@@ -7079,19 +7064,19 @@
     </row>
     <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B189" s="2">
         <v>1</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D189" s="2">
         <v>7</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F189" s="2">
         <v>4</v>
@@ -7109,19 +7094,19 @@
     </row>
     <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B190" s="2">
         <v>4</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D190" s="2">
         <v>7</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F190" s="2">
         <v>1</v>
@@ -7139,19 +7124,19 @@
     </row>
     <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B191" s="2">
         <v>4</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D191" s="2">
         <v>7</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F191" s="2">
         <v>1</v>
@@ -7169,19 +7154,19 @@
     </row>
     <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B192" s="2">
         <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D192" s="2">
         <v>7</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F192" s="2">
         <v>1</v>
@@ -7199,19 +7184,19 @@
     </row>
     <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B193" s="2">
         <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D193" s="2">
         <v>7</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F193" s="2">
         <v>1</v>
@@ -7229,19 +7214,19 @@
     </row>
     <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B194" s="2">
         <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D194" s="2">
         <v>7</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F194" s="2">
         <v>2</v>
@@ -7253,25 +7238,25 @@
         <v>64</v>
       </c>
       <c r="I194" s="2">
-        <f t="shared" ref="I194:I257" si="3">H194/G194</f>
+        <f t="shared" ref="I194:I220" si="3">H194/G194</f>
         <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B195" s="2">
         <v>2</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D195" s="2">
         <v>7</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F195" s="2">
         <v>5</v>
@@ -7289,19 +7274,19 @@
     </row>
     <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B196" s="2">
         <v>2</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D196" s="2">
         <v>7</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F196" s="2">
         <v>3</v>
@@ -7319,19 +7304,19 @@
     </row>
     <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B197" s="2">
         <v>3</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D197" s="2">
         <v>7</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F197" s="2">
         <v>3</v>
@@ -7349,19 +7334,19 @@
     </row>
     <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B198" s="2">
         <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D198" s="2">
         <v>7</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F198" s="2">
         <v>1</v>
@@ -7379,19 +7364,19 @@
     </row>
     <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B199" s="2">
         <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D199" s="2">
         <v>7</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F199" s="2">
         <v>1</v>
@@ -7409,19 +7394,19 @@
     </row>
     <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B200" s="2">
         <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D200" s="2">
         <v>7</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F200" s="2">
         <v>1</v>
@@ -7439,19 +7424,19 @@
     </row>
     <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B201" s="2">
         <v>3</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D201" s="2">
         <v>7</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F201" s="2">
         <v>2</v>
@@ -7469,19 +7454,19 @@
     </row>
     <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B202" s="2">
         <v>2</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D202" s="2">
         <v>7</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F202" s="2">
         <v>4</v>
@@ -7499,19 +7484,19 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B203" s="2">
         <v>2</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D203" s="2">
         <v>8</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F203" s="2">
         <v>2</v>
@@ -7529,19 +7514,19 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B204" s="2">
         <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D204" s="2">
         <v>8</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F204" s="2">
         <v>2</v>
@@ -7559,19 +7544,19 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B205" s="2">
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D205" s="2">
         <v>8</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F205" s="2">
         <v>1</v>
@@ -7589,19 +7574,19 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B206" s="2">
         <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D206" s="2">
         <v>8</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F206" s="2">
         <v>1</v>
@@ -7619,19 +7604,19 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B207" s="2">
         <v>1</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D207" s="2">
         <v>8</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F207" s="2">
         <v>2</v>
@@ -7649,19 +7634,19 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B208" s="2">
         <v>3</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D208" s="2">
         <v>8</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F208" s="2">
         <v>2</v>
@@ -7679,19 +7664,19 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B209" s="2">
         <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D209" s="2">
         <v>8</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F209" s="2">
         <v>2</v>
@@ -7709,19 +7694,19 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B210" s="2">
         <v>2</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D210" s="2">
         <v>8</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F210" s="2">
         <v>4</v>
@@ -7739,19 +7724,19 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B211" s="2">
         <v>3</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D211" s="2">
         <v>8</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F211" s="2">
         <v>3</v>
@@ -7769,19 +7754,19 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B212" s="2">
         <v>1</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D212" s="2">
         <v>8</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F212" s="2">
         <v>4</v>
@@ -7799,19 +7784,19 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B213" s="2">
         <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D213" s="2">
         <v>8</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F213" s="2">
         <v>1</v>
@@ -7829,19 +7814,19 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B214" s="2">
         <v>1</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D214" s="2">
         <v>8</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F214" s="2">
         <v>3</v>
@@ -7859,19 +7844,19 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B215" s="2">
         <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D215" s="2">
         <v>8</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F215" s="2">
         <v>2</v>
@@ -7889,19 +7874,19 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B216" s="2">
         <v>3</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D216" s="2">
         <v>8</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F216" s="2">
         <v>2</v>
@@ -7919,19 +7904,19 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B217" s="2">
         <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D217" s="2">
         <v>8</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F217" s="2">
         <v>1</v>
@@ -7949,19 +7934,19 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B218" s="2">
         <v>4</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D218" s="2">
         <v>8</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F218" s="2">
         <v>2</v>
@@ -7979,19 +7964,19 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B219" s="2">
         <v>4</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D219" s="2">
         <v>8</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F219" s="2">
         <v>1</v>
@@ -8009,19 +7994,19 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B220" s="2">
         <v>1</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D220" s="2">
         <v>8</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F220" s="2">
         <v>1</v>
@@ -8039,6 +8024,9 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I220">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -8050,9 +8038,6 @@
           <x14:id>{AABB7699-A00C-46C8-8502-19581232CD76}</x14:id>
         </ext>
       </extLst>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
-      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/department_schedules_finals/faculty_schedule_manuel_finals.xlsx
+++ b/data/department_schedules_finals/faculty_schedule_manuel_finals.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE160B1A-DA66-4368-8CFA-FFBF8E3025FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092FC85D-B834-4A06-9C84-189F56DD846D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35520" yWindow="13725" windowWidth="24465" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38505" yWindow="6060" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1099,9 +1099,10 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{33F8AAF9-828B-4703-A5CE-91BFA20E22FE}" name="Table1" displayName="Table1" ref="A1:I220" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
   <autoFilter ref="A1:I220" xr:uid="{33F8AAF9-828B-4703-A5CE-91BFA20E22FE}">
-    <filterColumn colId="3">
+    <filterColumn colId="0">
       <filters>
-        <filter val="8"/>
+        <filter val="BM"/>
+        <filter val="BM,EM"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1452,7 +1453,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -2322,7 +2323,7 @@
         <v>0.88636363636363635</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
@@ -2352,7 +2353,7 @@
         <v>0.75471698113207553</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>7</v>
       </c>
@@ -2382,7 +2383,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>7</v>
       </c>
@@ -2412,7 +2413,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>7</v>
       </c>
@@ -3042,7 +3043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
@@ -3192,7 +3193,7 @@
         <v>1.0192307692307692</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>7</v>
       </c>
@@ -3222,7 +3223,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>7</v>
       </c>
@@ -3252,7 +3253,7 @@
         <v>0.27500000000000002</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>7</v>
       </c>
@@ -3282,7 +3283,7 @@
         <v>0.99137931034482762</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>7</v>
       </c>
@@ -3402,7 +3403,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>17</v>
       </c>
@@ -3432,7 +3433,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>7</v>
       </c>
@@ -4122,7 +4123,7 @@
         <v>1.0978260869565217</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>17</v>
       </c>
@@ -4152,7 +4153,7 @@
         <v>0.6694444444444444</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>7</v>
       </c>
@@ -4182,7 +4183,7 @@
         <v>0.73170731707317072</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>7</v>
       </c>
@@ -5142,7 +5143,7 @@
         <v>0.65625</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>7</v>
       </c>
@@ -5202,7 +5203,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>7</v>
       </c>
@@ -5922,7 +5923,7 @@
         <v>1.076086956521739</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>7</v>
       </c>
@@ -6312,7 +6313,7 @@
         <v>0.68181818181818177</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>7</v>
       </c>
@@ -6462,7 +6463,7 @@
         <v>1.0434782608695652</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>7</v>
       </c>
@@ -6492,7 +6493,7 @@
         <v>0.97222222222222221</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>7</v>
       </c>
@@ -6612,7 +6613,7 @@
         <v>1.2903225806451613</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>7</v>
       </c>
@@ -7062,7 +7063,7 @@
         <v>1.0909090909090908</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>7</v>
       </c>
@@ -7332,7 +7333,7 @@
         <v>0.90217391304347827</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>7</v>
       </c>
@@ -7362,7 +7363,7 @@
         <v>1.125</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>7</v>
       </c>
@@ -7392,7 +7393,7 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>7</v>
       </c>
@@ -7452,7 +7453,7 @@
         <v>1.0694444444444444</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>7</v>
       </c>
@@ -7482,7 +7483,7 @@
         <v>0.50261780104712039</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>10</v>
       </c>
@@ -7512,7 +7513,7 @@
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>10</v>
       </c>
@@ -7542,7 +7543,7 @@
         <v>0.86904761904761907</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>10</v>
       </c>
@@ -7572,7 +7573,7 @@
         <v>1.0555555555555556</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>10</v>
       </c>
@@ -7602,7 +7603,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>15</v>
       </c>
@@ -7632,7 +7633,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>8</v>
       </c>
@@ -7662,7 +7663,7 @@
         <v>1.2586206896551724</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>8</v>
       </c>
@@ -7692,7 +7693,7 @@
         <v>1.2586206896551724</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>8</v>
       </c>
@@ -7782,7 +7783,7 @@
         <v>0.69109947643979053</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>12</v>
       </c>
@@ -7812,7 +7813,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>12</v>
       </c>
@@ -7842,7 +7843,7 @@
         <v>1.3369565217391304</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>12</v>
       </c>
@@ -7872,7 +7873,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>12</v>
       </c>
@@ -7902,7 +7903,7 @@
         <v>1.0277777777777777</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>12</v>
       </c>
@@ -7992,7 +7993,7 @@
         <v>0.57499999999999996</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>8</v>
       </c>

--- a/data/department_schedules_finals/faculty_schedule_manuel_finals.xlsx
+++ b/data/department_schedules_finals/faculty_schedule_manuel_finals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092FC85D-B834-4A06-9C84-189F56DD846D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3553A332-E4B7-48AE-A0F9-F45EB6556D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38505" yWindow="6060" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1098,14 +1098,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{33F8AAF9-828B-4703-A5CE-91BFA20E22FE}" name="Table1" displayName="Table1" ref="A1:I220" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
-  <autoFilter ref="A1:I220" xr:uid="{33F8AAF9-828B-4703-A5CE-91BFA20E22FE}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="BM"/>
-        <filter val="BM,EM"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I220" xr:uid="{33F8AAF9-828B-4703-A5CE-91BFA20E22FE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H220">
     <sortCondition ref="D1:D220"/>
   </sortState>
@@ -1418,7 +1411,7 @@
   <cols>
     <col min="1" max="1" width="13.6328125" customWidth="1"/>
     <col min="3" max="3" width="10.6328125" customWidth="1"/>
-    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+    <col min="5" max="5" width="32.26953125" customWidth="1"/>
     <col min="6" max="6" width="17.453125" customWidth="1"/>
     <col min="7" max="7" width="15.6328125" customWidth="1"/>
     <col min="8" max="8" width="14.54296875" customWidth="1"/>
@@ -1483,7 +1476,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1513,7 +1506,7 @@
         <v>1.2083333333333333</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -1543,7 +1536,7 @@
         <v>0.30555555555555558</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -1573,7 +1566,7 @@
         <v>0.3611111111111111</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1603,7 +1596,7 @@
         <v>0.19444444444444445</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -1633,7 +1626,7 @@
         <v>0.3611111111111111</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -1663,7 +1656,7 @@
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -1693,7 +1686,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1723,7 +1716,7 @@
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1753,7 +1746,7 @@
         <v>0.97619047619047616</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1783,7 +1776,7 @@
         <v>0.76190476190476186</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -1813,7 +1806,7 @@
         <v>0.6428571428571429</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -1843,7 +1836,7 @@
         <v>0.97499999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -1873,7 +1866,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -1903,7 +1896,7 @@
         <v>0.69117647058823528</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
@@ -1933,7 +1926,7 @@
         <v>0.7321428571428571</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
@@ -1963,7 +1956,7 @@
         <v>0.88571428571428568</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>8</v>
       </c>
@@ -1993,7 +1986,7 @@
         <v>1.0319148936170213</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>8</v>
       </c>
@@ -2023,7 +2016,7 @@
         <v>1.2068965517241379</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
@@ -2053,7 +2046,7 @@
         <v>0.86206896551724133</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
@@ -2083,7 +2076,7 @@
         <v>0.96153846153846156</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
@@ -2113,7 +2106,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
@@ -2143,7 +2136,7 @@
         <v>0.47499999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -2173,7 +2166,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>11</v>
       </c>
@@ -2203,7 +2196,7 @@
         <v>0.796875</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>11</v>
       </c>
@@ -2233,7 +2226,7 @@
         <v>1.0625</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>12</v>
       </c>
@@ -2263,7 +2256,7 @@
         <v>1.0681818181818181</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -2293,7 +2286,7 @@
         <v>0.99242424242424243</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>12</v>
       </c>
@@ -2443,7 +2436,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>11</v>
       </c>
@@ -2473,7 +2466,7 @@
         <v>0.67500000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>13</v>
       </c>
@@ -2503,7 +2496,7 @@
         <v>0.30555555555555558</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>13</v>
       </c>
@@ -2533,7 +2526,7 @@
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>13</v>
       </c>
@@ -2563,7 +2556,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>13</v>
       </c>
@@ -2593,7 +2586,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>9</v>
       </c>
@@ -2623,7 +2616,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>9</v>
       </c>
@@ -2653,7 +2646,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
@@ -2683,7 +2676,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
@@ -2713,7 +2706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>10</v>
       </c>
@@ -2743,7 +2736,7 @@
         <v>0.70238095238095233</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>10</v>
       </c>
@@ -2773,7 +2766,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -2803,7 +2796,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -2833,7 +2826,7 @@
         <v>1.0277777777777777</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
@@ -2863,7 +2856,7 @@
         <v>0.90909090909090906</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>8</v>
       </c>
@@ -2893,7 +2886,7 @@
         <v>0.55555555555555558</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>11</v>
       </c>
@@ -2923,7 +2916,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>14</v>
       </c>
@@ -2953,7 +2946,7 @@
         <v>1.1808510638297873</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>14</v>
       </c>
@@ -2983,7 +2976,7 @@
         <v>1.2446808510638299</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>8</v>
       </c>
@@ -3013,7 +3006,7 @@
         <v>0.63793103448275867</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>8</v>
       </c>
@@ -3073,7 +3066,7 @@
         <v>0.57534246575342463</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -3103,7 +3096,7 @@
         <v>0.47499999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>11</v>
       </c>
@@ -3133,7 +3126,7 @@
         <v>0.765625</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>11</v>
       </c>
@@ -3163,7 +3156,7 @@
         <v>0.96875</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>11</v>
       </c>
@@ -3313,7 +3306,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>12</v>
       </c>
@@ -3343,7 +3336,7 @@
         <v>0.26666666666666666</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -3373,7 +3366,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>12</v>
       </c>
@@ -3463,7 +3456,7 @@
         <v>0.54255319148936165</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>13</v>
       </c>
@@ -3493,7 +3486,7 @@
         <v>0.44444444444444442</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>13</v>
       </c>
@@ -3523,7 +3516,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>8</v>
       </c>
@@ -3553,7 +3546,7 @@
         <v>0.55555555555555558</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>13</v>
       </c>
@@ -3583,7 +3576,7 @@
         <v>0.52777777777777779</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>13</v>
       </c>
@@ -3613,7 +3606,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>9</v>
       </c>
@@ -3643,7 +3636,7 @@
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>9</v>
       </c>
@@ -3673,7 +3666,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>9</v>
       </c>
@@ -3703,7 +3696,7 @@
         <v>0.1388888888888889</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>9</v>
       </c>
@@ -3733,7 +3726,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>10</v>
       </c>
@@ -3763,7 +3756,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>10</v>
       </c>
@@ -3793,7 +3786,7 @@
         <v>0.51190476190476186</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -3823,7 +3816,7 @@
         <v>0.88888888888888884</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>11</v>
       </c>
@@ -3853,7 +3846,7 @@
         <v>0.3888888888888889</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>11</v>
       </c>
@@ -3883,7 +3876,7 @@
         <v>0.91428571428571426</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>8</v>
       </c>
@@ -3913,7 +3906,7 @@
         <v>0.85106382978723405</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>8</v>
       </c>
@@ -3943,7 +3936,7 @@
         <v>1.2931034482758621</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>8</v>
       </c>
@@ -3973,7 +3966,7 @@
         <v>1.4090909090909092</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>10</v>
       </c>
@@ -4003,7 +3996,7 @@
         <v>0.61643835616438358</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>12</v>
       </c>
@@ -4033,7 +4026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -4063,7 +4056,7 @@
         <v>0.953125</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>11</v>
       </c>
@@ -4093,7 +4086,7 @@
         <v>1.09375</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>12</v>
       </c>
@@ -4213,7 +4206,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>11</v>
       </c>
@@ -4243,7 +4236,7 @@
         <v>1.075</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>13</v>
       </c>
@@ -4273,7 +4266,7 @@
         <v>0.17857142857142858</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>13</v>
       </c>
@@ -4303,7 +4296,7 @@
         <v>0.52777777777777779</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>18</v>
       </c>
@@ -4333,7 +4326,7 @@
         <v>0.55555555555555558</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>13</v>
       </c>
@@ -4363,7 +4356,7 @@
         <v>0.1388888888888889</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>13</v>
       </c>
@@ -4393,7 +4386,7 @@
         <v>0.3888888888888889</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>13</v>
       </c>
@@ -4423,7 +4416,7 @@
         <v>0.27777777777777779</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>9</v>
       </c>
@@ -4453,7 +4446,7 @@
         <v>0.19444444444444445</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>9</v>
       </c>
@@ -4483,7 +4476,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
@@ -4513,7 +4506,7 @@
         <v>0.7583333333333333</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>10</v>
       </c>
@@ -4543,7 +4536,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>10</v>
       </c>
@@ -4573,7 +4566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>10</v>
       </c>
@@ -4603,7 +4596,7 @@
         <v>1.0833333333333333</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>10</v>
       </c>
@@ -4633,7 +4626,7 @@
         <v>1.0555555555555556</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>16</v>
       </c>
@@ -4663,7 +4656,7 @@
         <v>0.96296296296296291</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>11</v>
       </c>
@@ -4693,7 +4686,7 @@
         <v>0.3888888888888889</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>11</v>
       </c>
@@ -4723,7 +4716,7 @@
         <v>0.7592592592592593</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>8</v>
       </c>
@@ -4753,7 +4746,7 @@
         <v>1.0319148936170213</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>8</v>
       </c>
@@ -4783,7 +4776,7 @@
         <v>1.0454545454545454</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>9</v>
       </c>
@@ -4813,7 +4806,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>12</v>
       </c>
@@ -4843,7 +4836,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>12</v>
       </c>
@@ -4873,7 +4866,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>12</v>
       </c>
@@ -4903,7 +4896,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>12</v>
       </c>
@@ -4933,7 +4926,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>12</v>
       </c>
@@ -4963,7 +4956,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>11</v>
       </c>
@@ -4993,7 +4986,7 @@
         <v>0.859375</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>11</v>
       </c>
@@ -5023,7 +5016,7 @@
         <v>1.140625</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>11</v>
       </c>
@@ -5053,7 +5046,7 @@
         <v>1.09375</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>11</v>
       </c>
@@ -5083,7 +5076,7 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>12</v>
       </c>
@@ -5113,7 +5106,7 @@
         <v>1.076086956521739</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>12</v>
       </c>
@@ -5173,7 +5166,7 @@
         <v>0.99264705882352944</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>11</v>
       </c>
@@ -5233,7 +5226,7 @@
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>12</v>
       </c>
@@ -5263,7 +5256,7 @@
         <v>1.282258064516129</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>11</v>
       </c>
@@ -5293,7 +5286,7 @@
         <v>1.3012820512820513</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>11</v>
       </c>
@@ -5323,7 +5316,7 @@
         <v>0.99375000000000002</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>13</v>
       </c>
@@ -5353,7 +5346,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>13</v>
       </c>
@@ -5383,7 +5376,7 @@
         <v>0.3888888888888889</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>9</v>
       </c>
@@ -5413,7 +5406,7 @@
         <v>0.44444444444444442</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
@@ -5443,7 +5436,7 @@
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>9</v>
       </c>
@@ -5473,7 +5466,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>9</v>
       </c>
@@ -5503,7 +5496,7 @@
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>10</v>
       </c>
@@ -5533,7 +5526,7 @@
         <v>0.69047619047619047</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>10</v>
       </c>
@@ -5563,7 +5556,7 @@
         <v>0.77380952380952384</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>10</v>
       </c>
@@ -5593,7 +5586,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>10</v>
       </c>
@@ -5623,7 +5616,7 @@
         <v>1.0277777777777777</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>11</v>
       </c>
@@ -5653,7 +5646,7 @@
         <v>1.0285714285714285</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>8</v>
       </c>
@@ -5683,7 +5676,7 @@
         <v>1.1170212765957446</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>8</v>
       </c>
@@ -5713,7 +5706,7 @@
         <v>1.1489361702127661</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>8</v>
       </c>
@@ -5743,7 +5736,7 @@
         <v>0.89655172413793105</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>8</v>
       </c>
@@ -5773,7 +5766,7 @@
         <v>0.92307692307692313</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>12</v>
       </c>
@@ -5803,7 +5796,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>12</v>
       </c>
@@ -5833,7 +5826,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>11</v>
       </c>
@@ -5863,7 +5856,7 @@
         <v>0.890625</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>12</v>
       </c>
@@ -5893,7 +5886,7 @@
         <v>1.076086956521739</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>12</v>
       </c>
@@ -5953,7 +5946,7 @@
         <v>0.97115384615384615</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -5983,7 +5976,7 @@
         <v>1.40625</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>13</v>
       </c>
@@ -6013,7 +6006,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>9</v>
       </c>
@@ -6043,7 +6036,7 @@
         <v>0.19444444444444445</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>9</v>
       </c>
@@ -6073,7 +6066,7 @@
         <v>0.1388888888888889</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>10</v>
       </c>
@@ -6103,7 +6096,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>10</v>
       </c>
@@ -6133,7 +6126,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>10</v>
       </c>
@@ -6163,7 +6156,7 @@
         <v>1.0833333333333333</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -6193,7 +6186,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>11</v>
       </c>
@@ -6223,7 +6216,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>8</v>
       </c>
@@ -6253,7 +6246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>8</v>
       </c>
@@ -6283,7 +6276,7 @@
         <v>1.2727272727272727</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>8</v>
       </c>
@@ -6343,7 +6336,7 @@
         <v>0.76963350785340312</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>12</v>
       </c>
@@ -6373,7 +6366,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>12</v>
       </c>
@@ -6403,7 +6396,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>12</v>
       </c>
@@ -6433,7 +6426,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>12</v>
       </c>
@@ -6523,7 +6516,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>11</v>
       </c>
@@ -6553,7 +6546,7 @@
         <v>1.0694444444444444</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>8</v>
       </c>
@@ -6583,7 +6576,7 @@
         <v>0.65714285714285714</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>12</v>
       </c>
@@ -6643,7 +6636,7 @@
         <v>1.15625</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>13</v>
       </c>
@@ -6673,7 +6666,7 @@
         <v>0.19444444444444445</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>8</v>
       </c>
@@ -6703,7 +6696,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>13</v>
       </c>
@@ -6733,7 +6726,7 @@
         <v>0.61111111111111116</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>13</v>
       </c>
@@ -6763,7 +6756,7 @@
         <v>0.30555555555555558</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>9</v>
       </c>
@@ -6793,7 +6786,7 @@
         <v>0.1388888888888889</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>10</v>
       </c>
@@ -6823,7 +6816,7 @@
         <v>0.80833333333333335</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>10</v>
       </c>
@@ -6853,7 +6846,7 @@
         <v>0.80952380952380953</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>10</v>
       </c>
@@ -6883,7 +6876,7 @@
         <v>0.94047619047619047</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>10</v>
       </c>
@@ -6913,7 +6906,7 @@
         <v>0.80555555555555558</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>11</v>
       </c>
@@ -6943,7 +6936,7 @@
         <v>0.92142857142857137</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>8</v>
       </c>
@@ -6973,7 +6966,7 @@
         <v>1.1702127659574468</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>8</v>
       </c>
@@ -7003,7 +6996,7 @@
         <v>0.80769230769230771</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>8</v>
       </c>
@@ -7033,7 +7026,7 @@
         <v>1.0909090909090908</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>8</v>
       </c>
@@ -7093,7 +7086,7 @@
         <v>0.75916230366492143</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>12</v>
       </c>
@@ -7123,7 +7116,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>12</v>
       </c>
@@ -7153,7 +7146,7 @@
         <v>0.47499999999999998</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>12</v>
       </c>
@@ -7183,7 +7176,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>11</v>
       </c>
@@ -7213,7 +7206,7 @@
         <v>0.71875</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>11</v>
       </c>
@@ -7243,7 +7236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>11</v>
       </c>
@@ -7273,7 +7266,7 @@
         <v>0.92777777777777781</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>12</v>
       </c>
@@ -7303,7 +7296,7 @@
         <v>1.0543478260869565</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>12</v>
       </c>
@@ -7423,7 +7416,7 @@
         <v>0.47499999999999998</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>11</v>
       </c>
@@ -7483,7 +7476,7 @@
         <v>0.50261780104712039</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>10</v>
       </c>
@@ -7513,7 +7506,7 @@
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>10</v>
       </c>
@@ -7543,7 +7536,7 @@
         <v>0.86904761904761907</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>10</v>
       </c>
@@ -7573,7 +7566,7 @@
         <v>1.0555555555555556</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>10</v>
       </c>
@@ -7603,7 +7596,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>15</v>
       </c>
@@ -7633,7 +7626,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>8</v>
       </c>
@@ -7663,7 +7656,7 @@
         <v>1.2586206896551724</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>8</v>
       </c>
@@ -7693,7 +7686,7 @@
         <v>1.2586206896551724</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>8</v>
       </c>
@@ -7783,7 +7776,7 @@
         <v>0.69109947643979053</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>12</v>
       </c>
@@ -7813,7 +7806,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>12</v>
       </c>
@@ -7843,7 +7836,7 @@
         <v>1.3369565217391304</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>12</v>
       </c>
@@ -7873,7 +7866,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>12</v>
       </c>
@@ -7903,7 +7896,7 @@
         <v>1.0277777777777777</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>12</v>
       </c>
@@ -7993,7 +7986,7 @@
         <v>0.57499999999999996</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>8</v>
       </c>
